--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="208">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -550,16 +550,16 @@
     <t>BodyStructure.location</t>
   </si>
   <si>
-    <t>Body site</t>
+    <t>Localisation anatomique ou voie d'abord</t>
   </si>
   <si>
     <t>The anatomical location or region of the specimen, lesion, or body structure.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-location-body-structure-document</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -574,7 +574,7 @@
     <t>BodyStructure.locationQualifier</t>
   </si>
   <si>
-    <t>Body site modifier</t>
+    <t>Modificateurs topographiques</t>
   </si>
   <si>
     <t>Qualifier to refine the anatomical location.  These include qualifiers for laterality, relative location, directionality, number, and plane.</t>
@@ -987,8 +987,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.63671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.59375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="32.6484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2555,11 +2555,9 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y14" t="s" s="2">
         <v>174</v>
       </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
         <v>175</v>
       </c>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-body-structure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-body-structure-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
